--- a/test-files/preise.xlsx
+++ b/test-files/preise.xlsx
@@ -10,8 +10,18 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="#,##0.00\ &quot;€&quot;"/>
+    <numFmt numFmtId="165" formatCode="dd.mm.yyyy"/>
+  </numFmts>
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -37,8 +47,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
